--- a/pin.xlsx
+++ b/pin.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,14 +429,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>3827965705</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
-          <t>3827965705</t>
+          <t>4666846608</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1122</t>
         </is>
       </c>
     </row>

--- a/pin.xlsx
+++ b/pin.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,12 +429,20 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>2832693554</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
-          <t>2832693554</t>
+          <t>7983161650</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>1111</t>
         </is>
